--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123328780</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123328725</v>
+        <v>123334372</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419959</v>
+        <v>419916</v>
       </c>
       <c r="R3" t="n">
-        <v>6657089</v>
+        <v>6657053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123334372</v>
+        <v>123329861</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +896,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Borberget, Borberget, Vrm</t>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419916</v>
+        <v>419858</v>
       </c>
       <c r="R4" t="n">
-        <v>6657053</v>
+        <v>6657779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123329861</v>
+        <v>123334382</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>95914</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,43 +1003,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+          <t>Borberget, Borberget, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419858</v>
+        <v>419922</v>
       </c>
       <c r="R5" t="n">
-        <v>6657779</v>
+        <v>6657063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123334382</v>
+        <v>123328725</v>
       </c>
       <c r="B6" t="n">
-        <v>95911</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419922</v>
+        <v>419959</v>
       </c>
       <c r="R6" t="n">
-        <v>6657063</v>
+        <v>6657089</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123328780</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123334372</v>
+        <v>123329861</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borberget, Borberget, Vrm</t>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419916</v>
+        <v>419858</v>
       </c>
       <c r="R3" t="n">
-        <v>6657053</v>
+        <v>6657779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123329861</v>
+        <v>123334372</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+          <t>Borberget, Borberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419858</v>
+        <v>419916</v>
       </c>
       <c r="R4" t="n">
-        <v>6657779</v>
+        <v>6657053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123334382</v>
+        <v>123328725</v>
       </c>
       <c r="B5" t="n">
-        <v>95914</v>
+        <v>90957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419922</v>
+        <v>419959</v>
       </c>
       <c r="R5" t="n">
-        <v>6657063</v>
+        <v>6657089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123328725</v>
+        <v>123334382</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>95916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419959</v>
+        <v>419922</v>
       </c>
       <c r="R6" t="n">
-        <v>6657089</v>
+        <v>6657063</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123328780</v>
+        <v>123334372</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419987</v>
+        <v>419916</v>
       </c>
       <c r="R2" t="n">
-        <v>6657124</v>
+        <v>6657053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123334372</v>
+        <v>123334382</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>95922</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419916</v>
+        <v>419922</v>
       </c>
       <c r="R4" t="n">
-        <v>6657053</v>
+        <v>6657063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +994,7 @@
         <v>123328725</v>
       </c>
       <c r="B5" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123334382</v>
+        <v>123328780</v>
       </c>
       <c r="B6" t="n">
-        <v>95916</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419922</v>
+        <v>419987</v>
       </c>
       <c r="R6" t="n">
-        <v>6657063</v>
+        <v>6657124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123334372</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123329861</v>
+        <v>123328725</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>90966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+          <t>Borberget, Borberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419858</v>
+        <v>419959</v>
       </c>
       <c r="R3" t="n">
-        <v>6657779</v>
+        <v>6657089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +887,7 @@
         <v>123334382</v>
       </c>
       <c r="B4" t="n">
-        <v>95922</v>
+        <v>95925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123328725</v>
+        <v>123328780</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419959</v>
+        <v>419987</v>
       </c>
       <c r="R5" t="n">
-        <v>6657089</v>
+        <v>6657124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123328780</v>
+        <v>123329861</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1100,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Borberget, Borberget, Vrm</t>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419987</v>
+        <v>419858</v>
       </c>
       <c r="R6" t="n">
-        <v>6657124</v>
+        <v>6657779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123334372</v>
+        <v>123329861</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>5194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borberget, Borberget, Vrm</t>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419916</v>
+        <v>419858</v>
       </c>
       <c r="R2" t="n">
-        <v>6657053</v>
+        <v>6657779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123328725</v>
+        <v>123334382</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>95942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419959</v>
+        <v>419922</v>
       </c>
       <c r="R3" t="n">
-        <v>6657089</v>
+        <v>6657063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123334382</v>
+        <v>123334372</v>
       </c>
       <c r="B4" t="n">
-        <v>95925</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419922</v>
+        <v>419916</v>
       </c>
       <c r="R4" t="n">
-        <v>6657063</v>
+        <v>6657053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +994,7 @@
         <v>123328780</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123329861</v>
+        <v>123328725</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+          <t>Borberget, Borberget, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419858</v>
+        <v>419959</v>
       </c>
       <c r="R6" t="n">
-        <v>6657779</v>
+        <v>6657089</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123329861</v>
+        <v>123334372</v>
       </c>
       <c r="B2" t="n">
-        <v>5194</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+          <t>Borberget, Borberget, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419858</v>
+        <v>419916</v>
       </c>
       <c r="R2" t="n">
-        <v>6657779</v>
+        <v>6657053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>123334382</v>
       </c>
       <c r="B3" t="n">
-        <v>95942</v>
+        <v>95949</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123334372</v>
+        <v>123329861</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>5196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +896,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Borberget, Borberget, Vrm</t>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419916</v>
+        <v>419858</v>
       </c>
       <c r="R4" t="n">
-        <v>6657053</v>
+        <v>6657779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123328780</v>
+        <v>123328725</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>90988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419987</v>
+        <v>419959</v>
       </c>
       <c r="R5" t="n">
-        <v>6657124</v>
+        <v>6657089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123328725</v>
+        <v>123328780</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419959</v>
+        <v>419987</v>
       </c>
       <c r="R6" t="n">
-        <v>6657089</v>
+        <v>6657124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123334372</v>
+        <v>123328725</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419916</v>
+        <v>419959</v>
       </c>
       <c r="R2" t="n">
-        <v>6657053</v>
+        <v>6657089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123334382</v>
+        <v>123329861</v>
       </c>
       <c r="B3" t="n">
-        <v>95949</v>
+        <v>5196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borberget, Borberget, Vrm</t>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419922</v>
+        <v>419858</v>
       </c>
       <c r="R3" t="n">
-        <v>6657063</v>
+        <v>6657779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123329861</v>
+        <v>123328780</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+          <t>Borberget, Borberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419858</v>
+        <v>419987</v>
       </c>
       <c r="R4" t="n">
-        <v>6657779</v>
+        <v>6657124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123328725</v>
+        <v>123334382</v>
       </c>
       <c r="B5" t="n">
-        <v>90988</v>
+        <v>95951</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419959</v>
+        <v>419922</v>
       </c>
       <c r="R5" t="n">
-        <v>6657089</v>
+        <v>6657063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123328780</v>
+        <v>123334372</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419987</v>
+        <v>419916</v>
       </c>
       <c r="R6" t="n">
-        <v>6657124</v>
+        <v>6657053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123328725</v>
+        <v>123334382</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419959</v>
+        <v>419922</v>
       </c>
       <c r="R2" t="n">
-        <v>6657089</v>
+        <v>6657063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,55 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123329861</v>
+        <v>123328725</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+          <t>Borberget, Borberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419858</v>
+        <v>419959</v>
       </c>
       <c r="R3" t="n">
-        <v>6657779</v>
+        <v>6657089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123328780</v>
+        <v>123332402</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419987</v>
+        <v>419894</v>
       </c>
       <c r="R4" t="n">
-        <v>6657124</v>
+        <v>6657270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123334382</v>
+        <v>123328780</v>
       </c>
       <c r="B5" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419922</v>
+        <v>419987</v>
       </c>
       <c r="R5" t="n">
-        <v>6657063</v>
+        <v>6657124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123334372</v>
+        <v>16955250</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,17 +1091,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Borberget, Borberget, Vrm</t>
+          <t>Borberget, ca 200 m SO triangelpunkten, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419916</v>
+        <v>419910</v>
       </c>
       <c r="R6" t="n">
-        <v>6657053</v>
+        <v>6657054</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,19 +1140,19 @@
           <t>Norra Råda</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>S-Hag-0088</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2013-07-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
+          <t>2013-07-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1179,19 +1163,426 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog. Brant ostsluttning</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123334372</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Borberget, Borberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>419916</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6657053</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Råda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Återfynd. Barkborreangrepp och mycket död ved. Några björkar och enstaka granar skuggar fortfarande. Täta bestånd med bladrosetter spridda på minst två ställen</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Alexander Singer</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Alexander Singer</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123329754</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>419858</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6657712</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Råda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123329751</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>419859</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6657711</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Råda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123329861</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Risvålsmossen, Risvålsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>419858</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6657779</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Råda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123334382</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963604</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123328725</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123329754</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332402</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123329751</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963814</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967900</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963815</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964030</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970983</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123328780</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955801</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123329861</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2146,6 +2221,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965162</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2253,6 +2333,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959199</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2378,6 +2463,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16955250</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2480,6 +2570,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123334372</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2581,6 +2676,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959606</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2682,6 +2782,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966837</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2783,8 +2888,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969518</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54844-2024 artfynd.xlsx
+++ b/artfynd/A 54844-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>134963604</v>
       </c>
       <c r="B3" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>134963814</v>
       </c>
       <c r="B8" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>134967900</v>
       </c>
       <c r="B9" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>134963815</v>
       </c>
       <c r="B10" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>134964030</v>
       </c>
       <c r="B11" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>134970983</v>
       </c>
       <c r="B12" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>134955801</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>134959199</v>
       </c>
       <c r="B17" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>134959606</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>134966837</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>134969518</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
